--- a/output/Tables/2019/HIA_per_age_Rubin.xlsx
+++ b/output/Tables/2019/HIA_per_age_Rubin.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>448.857</v>
+        <v>450.468</v>
       </c>
       <c r="D2">
-        <v>404.061</v>
+        <v>405.626</v>
       </c>
       <c r="E2">
-        <v>493.654</v>
+        <v>495.31</v>
       </c>
       <c r="F2">
-        <v>25664.448</v>
+        <v>25762.1</v>
       </c>
       <c r="G2">
-        <v>23137.392</v>
+        <v>23231.785</v>
       </c>
       <c r="H2">
-        <v>28191.504</v>
+        <v>28292.416</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>3413371636.644</v>
+        <v>3426359308.911</v>
       </c>
       <c r="M2">
-        <v>3077273177.779</v>
+        <v>3089827354.54</v>
       </c>
       <c r="N2">
-        <v>3749470095.508</v>
+        <v>3762891263.282</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>862.232</v>
+        <v>868.513</v>
       </c>
       <c r="D3">
-        <v>785.706</v>
+        <v>791.576</v>
       </c>
       <c r="E3">
-        <v>938.758</v>
+        <v>945.451</v>
       </c>
       <c r="F3">
-        <v>40127.098</v>
+        <v>40414.242</v>
       </c>
       <c r="G3">
-        <v>36671.604</v>
+        <v>36939.9</v>
       </c>
       <c r="H3">
-        <v>43582.593</v>
+        <v>43888.583</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>5336904064.02</v>
+        <v>5375094128.631</v>
       </c>
       <c r="M3">
-        <v>4877323265.686</v>
+        <v>4913006686.786</v>
       </c>
       <c r="N3">
-        <v>5796484862.354</v>
+        <v>5837181570.476</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>2289.38</v>
+        <v>2313.768</v>
       </c>
       <c r="D4">
-        <v>2095.817</v>
+        <v>2114.198</v>
       </c>
       <c r="E4">
-        <v>2482.943</v>
+        <v>2513.338</v>
       </c>
       <c r="F4">
-        <v>85010.749</v>
+        <v>85887.20600000001</v>
       </c>
       <c r="G4">
-        <v>77982.94500000001</v>
+        <v>78647.952</v>
       </c>
       <c r="H4">
-        <v>92038.554</v>
+        <v>93126.461</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>11306429677.133</v>
+        <v>11422998462.233</v>
       </c>
       <c r="M4">
-        <v>10371731654.105</v>
+        <v>10460177628.167</v>
       </c>
       <c r="N4">
-        <v>12241127700.161</v>
+        <v>12385819296.3</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>4888.423</v>
+        <v>4889.279</v>
       </c>
       <c r="D5">
-        <v>4509.489</v>
+        <v>4510.361</v>
       </c>
       <c r="E5">
-        <v>5267.358</v>
+        <v>5268.197</v>
       </c>
       <c r="F5">
-        <v>131628.436</v>
+        <v>131630.88</v>
       </c>
       <c r="G5">
-        <v>121860.417</v>
+        <v>121863.918</v>
       </c>
       <c r="H5">
-        <v>141396.455</v>
+        <v>141397.843</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>17506581964.512</v>
+        <v>17506907073.951</v>
       </c>
       <c r="M5">
-        <v>16207435416.793</v>
+        <v>16207901049.258</v>
       </c>
       <c r="N5">
-        <v>18805728512.23</v>
+        <v>18805913098.645</v>
       </c>
     </row>
     <row r="6">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C6">
-        <v>10426.338</v>
+        <v>10474.488</v>
       </c>
       <c r="D6">
-        <v>9654.411</v>
+        <v>9700.778</v>
       </c>
       <c r="E6">
-        <v>11198.266</v>
+        <v>11248.198</v>
       </c>
       <c r="F6">
-        <v>178192.619</v>
+        <v>178798.114</v>
       </c>
       <c r="G6">
-        <v>165610.393</v>
+        <v>166201.989</v>
       </c>
       <c r="H6">
-        <v>190774.845</v>
+        <v>191394.239</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>23699618325.084</v>
+        <v>23780149184.565</v>
       </c>
       <c r="M6">
-        <v>22026182224.281</v>
+        <v>22104864547.14</v>
       </c>
       <c r="N6">
-        <v>25373054425.887</v>
+        <v>25455433821.989</v>
       </c>
     </row>
     <row r="7">
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>16759.41</v>
+        <v>16764.82</v>
       </c>
       <c r="D7">
-        <v>15372.803</v>
+        <v>15377.286</v>
       </c>
       <c r="E7">
-        <v>18146.016</v>
+        <v>18152.354</v>
       </c>
       <c r="F7">
-        <v>124294.685</v>
+        <v>124329.441</v>
       </c>
       <c r="G7">
-        <v>115253.862</v>
+        <v>115284.935</v>
       </c>
       <c r="H7">
-        <v>133335.508</v>
+        <v>133373.946</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>16531193115.848</v>
+        <v>16535815601.577</v>
       </c>
       <c r="M7">
-        <v>15328763694.42</v>
+        <v>15332896321.082</v>
       </c>
       <c r="N7">
-        <v>17733622537.276</v>
+        <v>17738734882.073</v>
       </c>
     </row>
     <row r="8">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>22824.043</v>
+        <v>23163.833</v>
       </c>
       <c r="D8">
-        <v>20295.324</v>
+        <v>20583.601</v>
       </c>
       <c r="E8">
-        <v>25352.761</v>
+        <v>25744.066</v>
       </c>
       <c r="F8">
-        <v>19972.496</v>
+        <v>20137.822</v>
       </c>
       <c r="G8">
-        <v>16870.185</v>
+        <v>17030.804</v>
       </c>
       <c r="H8">
-        <v>23074.807</v>
+        <v>23244.84</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>2656341973.283</v>
+        <v>2678330275.687</v>
       </c>
       <c r="M8">
-        <v>2243734630.471</v>
+        <v>2265096879.666</v>
       </c>
       <c r="N8">
-        <v>3068949316.095</v>
+        <v>3091563671.709</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>231.497</v>
+        <v>234.716</v>
       </c>
       <c r="D9">
-        <v>206.325</v>
+        <v>209.214</v>
       </c>
       <c r="E9">
-        <v>256.67</v>
+        <v>260.218</v>
       </c>
       <c r="F9">
-        <v>877.853</v>
+        <v>886.468</v>
       </c>
       <c r="G9">
-        <v>781.835</v>
+        <v>789.725</v>
       </c>
       <c r="H9">
-        <v>973.87</v>
+        <v>983.21</v>
       </c>
       <c r="I9">
-        <v>12894872.445</v>
+        <v>13074137.71</v>
       </c>
       <c r="J9">
-        <v>11492730.942</v>
+        <v>11653620.506</v>
       </c>
       <c r="K9">
-        <v>14297013.947</v>
+        <v>14494654.913</v>
       </c>
       <c r="L9">
-        <v>116754390.141</v>
+        <v>117900187.086</v>
       </c>
       <c r="M9">
-        <v>103984058.216</v>
+        <v>105033379.758</v>
       </c>
       <c r="N9">
-        <v>129524722.067</v>
+        <v>130766994.415</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>481.237</v>
+        <v>490.129</v>
       </c>
       <c r="D10">
-        <v>434.345</v>
+        <v>442.671</v>
       </c>
       <c r="E10">
-        <v>528.129</v>
+        <v>537.588</v>
       </c>
       <c r="F10">
-        <v>1504.136</v>
+        <v>1524.596</v>
       </c>
       <c r="G10">
-        <v>1357.352</v>
+        <v>1376.936</v>
       </c>
       <c r="H10">
-        <v>1650.92</v>
+        <v>1672.256</v>
       </c>
       <c r="I10">
-        <v>26805858.867</v>
+        <v>27301181.399</v>
       </c>
       <c r="J10">
-        <v>24193876.893</v>
+        <v>24657649.238</v>
       </c>
       <c r="K10">
-        <v>29417840.841</v>
+        <v>29944713.561</v>
       </c>
       <c r="L10">
-        <v>200050066.378</v>
+        <v>202771277.687</v>
       </c>
       <c r="M10">
-        <v>180527838.816</v>
+        <v>183132512.063</v>
       </c>
       <c r="N10">
-        <v>219572293.939</v>
+        <v>222410043.31</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1648.333</v>
+        <v>1696.728</v>
       </c>
       <c r="D11">
-        <v>1488.037</v>
+        <v>1526.361</v>
       </c>
       <c r="E11">
-        <v>1808.629</v>
+        <v>1867.096</v>
       </c>
       <c r="F11">
-        <v>4121.652</v>
+        <v>4221.09</v>
       </c>
       <c r="G11">
-        <v>3714.986</v>
+        <v>3793.413</v>
       </c>
       <c r="H11">
-        <v>4528.317</v>
+        <v>4648.767</v>
       </c>
       <c r="I11">
-        <v>91815461.36</v>
+        <v>94511166.69599999</v>
       </c>
       <c r="J11">
-        <v>82886649.63699999</v>
+        <v>85021366.551</v>
       </c>
       <c r="K11">
-        <v>100744273.083</v>
+        <v>104000966.841</v>
       </c>
       <c r="L11">
-        <v>548179662.375</v>
+        <v>561404922.712</v>
       </c>
       <c r="M11">
-        <v>494093101.95</v>
+        <v>504523894.08</v>
       </c>
       <c r="N11">
-        <v>602266222.799</v>
+        <v>618285951.344</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>3824.068</v>
+        <v>3880.736</v>
       </c>
       <c r="D12">
-        <v>3495.531</v>
+        <v>3548.037</v>
       </c>
       <c r="E12">
-        <v>4152.604</v>
+        <v>4213.435</v>
       </c>
       <c r="F12">
-        <v>6910.842</v>
+        <v>6986.253</v>
       </c>
       <c r="G12">
-        <v>6321.071</v>
+        <v>6390.645</v>
       </c>
       <c r="H12">
-        <v>7500.612</v>
+        <v>7581.861</v>
       </c>
       <c r="I12">
-        <v>213008214.593</v>
+        <v>216164754.847</v>
       </c>
       <c r="J12">
-        <v>194708060.158</v>
+        <v>197632738.267</v>
       </c>
       <c r="K12">
-        <v>231308369.027</v>
+        <v>234696771.428</v>
       </c>
       <c r="L12">
-        <v>919141935.568</v>
+        <v>929171620.182</v>
       </c>
       <c r="M12">
-        <v>840702416.056</v>
+        <v>849955775.275</v>
       </c>
       <c r="N12">
-        <v>997581455.08</v>
+        <v>1008387465.09</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>11571.624</v>
+        <v>11712.422</v>
       </c>
       <c r="D13">
-        <v>10632.911</v>
+        <v>10769.859</v>
       </c>
       <c r="E13">
-        <v>12510.337</v>
+        <v>12654.984</v>
       </c>
       <c r="F13">
-        <v>13758.267</v>
+        <v>13862.475</v>
       </c>
       <c r="G13">
-        <v>12635.602</v>
+        <v>12737.3</v>
       </c>
       <c r="H13">
-        <v>14880.931</v>
+        <v>14987.65</v>
       </c>
       <c r="I13">
-        <v>644562591.0420001</v>
+        <v>652405304.904</v>
       </c>
       <c r="J13">
-        <v>592274385.443</v>
+        <v>599902667.47</v>
       </c>
       <c r="K13">
-        <v>696850796.64</v>
+        <v>704907942.3380001</v>
       </c>
       <c r="L13">
-        <v>1829849469.729</v>
+        <v>1843709199.381</v>
       </c>
       <c r="M13">
-        <v>1680535069.765</v>
+        <v>1694060914.898</v>
       </c>
       <c r="N13">
-        <v>1979163869.693</v>
+        <v>1993357483.864</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>13476.493</v>
+        <v>13598.257</v>
       </c>
       <c r="D14">
-        <v>12346.944</v>
+        <v>12460.343</v>
       </c>
       <c r="E14">
-        <v>14606.043</v>
+        <v>14736.171</v>
       </c>
       <c r="F14">
-        <v>7965.927</v>
+        <v>8004.189</v>
       </c>
       <c r="G14">
-        <v>7255.466</v>
+        <v>7292.748</v>
       </c>
       <c r="H14">
-        <v>8676.388000000001</v>
+        <v>8715.629999999999</v>
       </c>
       <c r="I14">
-        <v>750667622.188</v>
+        <v>757450121.765</v>
       </c>
       <c r="J14">
-        <v>687749448.295</v>
+        <v>694066047.489</v>
       </c>
       <c r="K14">
-        <v>813585796.082</v>
+        <v>820834196.0420001</v>
       </c>
       <c r="L14">
-        <v>1059468287.269</v>
+        <v>1064557138.908</v>
       </c>
       <c r="M14">
-        <v>964976981.6799999</v>
+        <v>969935431.303</v>
       </c>
       <c r="N14">
-        <v>1153959592.858</v>
+        <v>1159178846.513</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>8920.395</v>
+        <v>9078.575000000001</v>
       </c>
       <c r="D15">
-        <v>7836.114</v>
+        <v>7983.545</v>
       </c>
       <c r="E15">
-        <v>10004.676</v>
+        <v>10173.604</v>
       </c>
       <c r="F15">
-        <v>800.289</v>
+        <v>807.12</v>
       </c>
       <c r="G15">
-        <v>649.433</v>
+        <v>656.401</v>
       </c>
       <c r="H15">
-        <v>951.145</v>
+        <v>957.8390000000001</v>
       </c>
       <c r="I15">
-        <v>496883839.295</v>
+        <v>505694777.718</v>
       </c>
       <c r="J15">
-        <v>436487228.615</v>
+        <v>444699443.631</v>
       </c>
       <c r="K15">
-        <v>557280449.975</v>
+        <v>566690111.804</v>
       </c>
       <c r="L15">
-        <v>106438473.999</v>
+        <v>107346957.88</v>
       </c>
       <c r="M15">
-        <v>86374637.06999999</v>
+        <v>87301277.20100001</v>
       </c>
       <c r="N15">
-        <v>126502310.929</v>
+        <v>127392638.559</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>1956.365</v>
+        <v>1874.359</v>
       </c>
       <c r="D16">
-        <v>1631.443</v>
+        <v>1584.59</v>
       </c>
       <c r="E16">
-        <v>2281.287</v>
+        <v>2164.129</v>
       </c>
       <c r="F16">
-        <v>6598.776</v>
+        <v>6327.123</v>
       </c>
       <c r="G16">
-        <v>5473.424</v>
+        <v>5324.072</v>
       </c>
       <c r="H16">
-        <v>7724.127</v>
+        <v>7330.173</v>
       </c>
       <c r="I16">
-        <v>28967895.9</v>
+        <v>27753639.176</v>
       </c>
       <c r="J16">
-        <v>24156776.957</v>
+        <v>23463018.138</v>
       </c>
       <c r="K16">
-        <v>33779014.842</v>
+        <v>32044260.213</v>
       </c>
       <c r="L16">
-        <v>877637153.942</v>
+        <v>841507329.159</v>
       </c>
       <c r="M16">
-        <v>727965382.169</v>
+        <v>708101585.302</v>
       </c>
       <c r="N16">
-        <v>1027308925.715</v>
+        <v>974913073.016</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>3344.961</v>
+        <v>3207.574</v>
       </c>
       <c r="D17">
-        <v>2824.49</v>
+        <v>2741.753</v>
       </c>
       <c r="E17">
-        <v>3865.432</v>
+        <v>3673.395</v>
       </c>
       <c r="F17">
-        <v>9468.994000000001</v>
+        <v>9088.564</v>
       </c>
       <c r="G17">
-        <v>7956.093</v>
+        <v>7735.067</v>
       </c>
       <c r="H17">
-        <v>10981.896</v>
+        <v>10442.061</v>
       </c>
       <c r="I17">
-        <v>49528835.39</v>
+        <v>47494548.472</v>
       </c>
       <c r="J17">
-        <v>41822221.612</v>
+        <v>40597134.325</v>
       </c>
       <c r="K17">
-        <v>57235449.168</v>
+        <v>54391962.619</v>
       </c>
       <c r="L17">
-        <v>1259376263.648</v>
+        <v>1208779033.84</v>
       </c>
       <c r="M17">
-        <v>1058160318.905</v>
+        <v>1028763909.844</v>
       </c>
       <c r="N17">
-        <v>1460592208.391</v>
+        <v>1388794157.836</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>4376.991</v>
+        <v>4263.157</v>
       </c>
       <c r="D18">
-        <v>3758.446</v>
+        <v>3704.202</v>
       </c>
       <c r="E18">
-        <v>4995.537</v>
+        <v>4822.111</v>
       </c>
       <c r="F18">
-        <v>9969.606</v>
+        <v>9720.277</v>
       </c>
       <c r="G18">
-        <v>8485.638999999999</v>
+        <v>8379.331</v>
       </c>
       <c r="H18">
-        <v>11453.572</v>
+        <v>11061.224</v>
       </c>
       <c r="I18">
-        <v>64810112.811</v>
+        <v>63124562.685</v>
       </c>
       <c r="J18">
-        <v>55651304.202</v>
+        <v>54848122.829</v>
       </c>
       <c r="K18">
-        <v>73968921.419</v>
+        <v>71401002.54099999</v>
       </c>
       <c r="L18">
-        <v>1325957573.164</v>
+        <v>1292796899.266</v>
       </c>
       <c r="M18">
-        <v>1128590032.129</v>
+        <v>1114450982.353</v>
       </c>
       <c r="N18">
-        <v>1523325114.199</v>
+        <v>1471142816.178</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>5694.146</v>
+        <v>5446.525</v>
       </c>
       <c r="D19">
-        <v>5010.677</v>
+        <v>4836.711</v>
       </c>
       <c r="E19">
-        <v>6377.616</v>
+        <v>6056.338</v>
       </c>
       <c r="F19">
-        <v>9344.888999999999</v>
+        <v>8945.675999999999</v>
       </c>
       <c r="G19">
-        <v>8175.225</v>
+        <v>7899.928</v>
       </c>
       <c r="H19">
-        <v>10514.553</v>
+        <v>9991.424999999999</v>
       </c>
       <c r="I19">
-        <v>84313225.148</v>
+        <v>80646694.008</v>
       </c>
       <c r="J19">
-        <v>74193090.84999999</v>
+        <v>71617185.62800001</v>
       </c>
       <c r="K19">
-        <v>94433359.44499999</v>
+        <v>89676202.389</v>
       </c>
       <c r="L19">
-        <v>1242870234.178</v>
+        <v>1189774930.996</v>
       </c>
       <c r="M19">
-        <v>1087304981.331</v>
+        <v>1050690396.01</v>
       </c>
       <c r="N19">
-        <v>1398435487.025</v>
+        <v>1328859465.981</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>8237.906999999999</v>
+        <v>8069.412</v>
       </c>
       <c r="D20">
-        <v>7396.088</v>
+        <v>7311.197</v>
       </c>
       <c r="E20">
-        <v>9079.727000000001</v>
+        <v>8827.627</v>
       </c>
       <c r="F20">
-        <v>8766.402</v>
+        <v>8587.796</v>
       </c>
       <c r="G20">
-        <v>7841.835</v>
+        <v>7751.862</v>
       </c>
       <c r="H20">
-        <v>9690.969999999999</v>
+        <v>9423.73</v>
       </c>
       <c r="I20">
-        <v>121978694.253</v>
+        <v>119483787.571</v>
       </c>
       <c r="J20">
-        <v>109513877.119</v>
+        <v>108256894.886</v>
       </c>
       <c r="K20">
-        <v>134443511.388</v>
+        <v>130710680.256</v>
       </c>
       <c r="L20">
-        <v>1165931490.962</v>
+        <v>1142176891.101</v>
       </c>
       <c r="M20">
-        <v>1042964012.479</v>
+        <v>1030997651.373</v>
       </c>
       <c r="N20">
-        <v>1288898969.445</v>
+        <v>1253356130.83</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>5443.025</v>
+        <v>5268.879</v>
       </c>
       <c r="D21">
-        <v>4824.552</v>
+        <v>4712.767</v>
       </c>
       <c r="E21">
-        <v>6061.498</v>
+        <v>5824.99</v>
       </c>
       <c r="F21">
-        <v>2759.39</v>
+        <v>2671.474</v>
       </c>
       <c r="G21">
-        <v>2428.202</v>
+        <v>2373.559</v>
       </c>
       <c r="H21">
-        <v>3090.578</v>
+        <v>2969.388</v>
       </c>
       <c r="I21">
-        <v>80594868.279</v>
+        <v>78016287.76100001</v>
       </c>
       <c r="J21">
-        <v>71437135.88</v>
+        <v>69781944.177</v>
       </c>
       <c r="K21">
-        <v>89752600.678</v>
+        <v>86250631.346</v>
       </c>
       <c r="L21">
-        <v>366998838.964</v>
+        <v>355305978.865</v>
       </c>
       <c r="M21">
-        <v>322950805.303</v>
+        <v>315683309.65</v>
       </c>
       <c r="N21">
-        <v>411046872.625</v>
+        <v>394928648.081</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>2159.334</v>
+        <v>2099.613</v>
       </c>
       <c r="D22">
-        <v>1780.812</v>
+        <v>1753.642</v>
       </c>
       <c r="E22">
-        <v>2537.857</v>
+        <v>2445.584</v>
       </c>
       <c r="F22">
-        <v>144.702</v>
+        <v>137.601</v>
       </c>
       <c r="G22">
-        <v>110.104</v>
+        <v>107.192</v>
       </c>
       <c r="H22">
-        <v>179.3</v>
+        <v>168.01</v>
       </c>
       <c r="I22">
-        <v>31973264.929</v>
+        <v>31088975.147</v>
       </c>
       <c r="J22">
-        <v>26368487.656</v>
+        <v>25966182.995</v>
       </c>
       <c r="K22">
-        <v>37578042.203</v>
+        <v>36211767.299</v>
       </c>
       <c r="L22">
-        <v>19245382.89</v>
+        <v>18300883.25</v>
       </c>
       <c r="M22">
-        <v>14643805.581</v>
+        <v>14256491.16</v>
       </c>
       <c r="N22">
-        <v>23846960.2</v>
+        <v>22345275.341</v>
       </c>
     </row>
     <row r="23">
@@ -1446,40 +1446,40 @@
         </is>
       </c>
       <c r="C23">
-        <v>402.67</v>
+        <v>406.088</v>
       </c>
       <c r="D23">
-        <v>346.313</v>
+        <v>354.034</v>
       </c>
       <c r="E23">
-        <v>459.026</v>
+        <v>458.141</v>
       </c>
       <c r="F23">
-        <v>1625.2</v>
+        <v>1634.356</v>
       </c>
       <c r="G23">
-        <v>1394.729</v>
+        <v>1421.893</v>
       </c>
       <c r="H23">
-        <v>1855.67</v>
+        <v>1846.819</v>
       </c>
       <c r="I23">
-        <v>30281167.866</v>
+        <v>30538206.47</v>
       </c>
       <c r="J23">
-        <v>26043084.613</v>
+        <v>26623732.802</v>
       </c>
       <c r="K23">
-        <v>34519251.118</v>
+        <v>34452680.138</v>
       </c>
       <c r="L23">
-        <v>216151538.287</v>
+        <v>217369361.393</v>
       </c>
       <c r="M23">
-        <v>185499018.544</v>
+        <v>189111819.54</v>
       </c>
       <c r="N23">
-        <v>246804058.029</v>
+        <v>245626903.246</v>
       </c>
     </row>
     <row r="24">
@@ -1494,40 +1494,40 @@
         </is>
       </c>
       <c r="C24">
-        <v>645.063</v>
+        <v>658.669</v>
       </c>
       <c r="D24">
-        <v>560.08</v>
+        <v>580.042</v>
       </c>
       <c r="E24">
-        <v>730.047</v>
+        <v>737.297</v>
       </c>
       <c r="F24">
-        <v>2147.34</v>
+        <v>2186.06</v>
       </c>
       <c r="G24">
-        <v>1861.745</v>
+        <v>1921.615</v>
       </c>
       <c r="H24">
-        <v>2432.934</v>
+        <v>2450.504</v>
       </c>
       <c r="I24">
-        <v>48509415.258</v>
+        <v>49532595.314</v>
       </c>
       <c r="J24">
-        <v>42118586.733</v>
+        <v>43619754.883</v>
       </c>
       <c r="K24">
-        <v>54900243.783</v>
+        <v>55445435.745</v>
       </c>
       <c r="L24">
-        <v>285596176.371</v>
+        <v>290745914.382</v>
       </c>
       <c r="M24">
-        <v>247612133.925</v>
+        <v>255574793.163</v>
       </c>
       <c r="N24">
-        <v>323580218.816</v>
+        <v>325917035.601</v>
       </c>
     </row>
     <row r="25">
@@ -1542,40 +1542,40 @@
         </is>
       </c>
       <c r="C25">
-        <v>956.91</v>
+        <v>983.914</v>
       </c>
       <c r="D25">
-        <v>833.918</v>
+        <v>864.652</v>
       </c>
       <c r="E25">
-        <v>1079.903</v>
+        <v>1103.176</v>
       </c>
       <c r="F25">
-        <v>2536.546</v>
+        <v>2597.435</v>
       </c>
       <c r="G25">
-        <v>2204.484</v>
+        <v>2278.214</v>
       </c>
       <c r="H25">
-        <v>2868.607</v>
+        <v>2916.655</v>
       </c>
       <c r="I25">
-        <v>71960611.73</v>
+        <v>73991305.87800001</v>
       </c>
       <c r="J25">
-        <v>62711448.656</v>
+        <v>65022695.461</v>
       </c>
       <c r="K25">
-        <v>81209774.80400001</v>
+        <v>82959916.296</v>
       </c>
       <c r="L25">
-        <v>337360564.343</v>
+        <v>345458847.18</v>
       </c>
       <c r="M25">
-        <v>293196368.534</v>
+        <v>303002517.959</v>
       </c>
       <c r="N25">
-        <v>381524760.153</v>
+        <v>387915176.402</v>
       </c>
     </row>
     <row r="26">
@@ -1590,40 +1590,40 @@
         </is>
       </c>
       <c r="C26">
-        <v>1515.731</v>
+        <v>1514.552</v>
       </c>
       <c r="D26">
-        <v>1346.652</v>
+        <v>1361.019</v>
       </c>
       <c r="E26">
-        <v>1684.809</v>
+        <v>1668.085</v>
       </c>
       <c r="F26">
-        <v>2933.855</v>
+        <v>2922.042</v>
       </c>
       <c r="G26">
-        <v>2603.312</v>
+        <v>2623.041</v>
       </c>
       <c r="H26">
-        <v>3264.397</v>
+        <v>3221.044</v>
       </c>
       <c r="I26">
-        <v>113984453.53</v>
+        <v>113895818.304</v>
       </c>
       <c r="J26">
-        <v>101269559.258</v>
+        <v>102349979.01</v>
       </c>
       <c r="K26">
-        <v>126699347.801</v>
+        <v>125441657.598</v>
       </c>
       <c r="L26">
-        <v>390202666.857</v>
+        <v>388631629.378</v>
       </c>
       <c r="M26">
-        <v>346240469.36</v>
+        <v>348864447.404</v>
       </c>
       <c r="N26">
-        <v>434164864.354</v>
+        <v>428398811.353</v>
       </c>
     </row>
     <row r="27">
@@ -1638,40 +1638,40 @@
         </is>
       </c>
       <c r="C27">
-        <v>2163.509</v>
+        <v>2178.529</v>
       </c>
       <c r="D27">
-        <v>1943.636</v>
+        <v>1978.309</v>
       </c>
       <c r="E27">
-        <v>2383.381</v>
+        <v>2378.749</v>
       </c>
       <c r="F27">
-        <v>2803.173</v>
+        <v>2807.034</v>
       </c>
       <c r="G27">
-        <v>2512.016</v>
+        <v>2543.399</v>
       </c>
       <c r="H27">
-        <v>3094.329</v>
+        <v>3070.67</v>
       </c>
       <c r="I27">
-        <v>162698016.164</v>
+        <v>163827582.305</v>
       </c>
       <c r="J27">
-        <v>146163400.835</v>
+        <v>148770838.926</v>
       </c>
       <c r="K27">
-        <v>179232631.493</v>
+        <v>178884325.684</v>
       </c>
       <c r="L27">
-        <v>372821947.698</v>
+        <v>373335563.358</v>
       </c>
       <c r="M27">
-        <v>334098113.291</v>
+        <v>338272022.669</v>
       </c>
       <c r="N27">
-        <v>411545782.104</v>
+        <v>408399104.048</v>
       </c>
     </row>
     <row r="28">
@@ -1686,40 +1686,40 @@
         </is>
       </c>
       <c r="C28">
-        <v>696.381</v>
+        <v>697.8440000000001</v>
       </c>
       <c r="D28">
-        <v>619.347</v>
+        <v>627.596</v>
       </c>
       <c r="E28">
-        <v>773.414</v>
+        <v>768.092</v>
       </c>
       <c r="F28">
-        <v>460.532</v>
+        <v>458.924</v>
       </c>
       <c r="G28">
-        <v>404.1</v>
+        <v>408.148</v>
       </c>
       <c r="H28">
-        <v>516.9640000000001</v>
+        <v>509.701</v>
       </c>
       <c r="I28">
-        <v>52368519.929</v>
+        <v>52478563.195</v>
       </c>
       <c r="J28">
-        <v>46575537.956</v>
+        <v>47195833.937</v>
       </c>
       <c r="K28">
-        <v>58161501.901</v>
+        <v>57761292.452</v>
       </c>
       <c r="L28">
-        <v>61250793.067</v>
+        <v>61036936.274</v>
       </c>
       <c r="M28">
-        <v>53745317.174</v>
+        <v>54283664.185</v>
       </c>
       <c r="N28">
-        <v>68756268.961</v>
+        <v>67790208.36300001</v>
       </c>
     </row>
     <row r="29">
@@ -1734,40 +1734,40 @@
         </is>
       </c>
       <c r="C29">
-        <v>27.762</v>
+        <v>28.273</v>
       </c>
       <c r="D29">
-        <v>23.201</v>
+        <v>24.069</v>
       </c>
       <c r="E29">
-        <v>32.323</v>
+        <v>32.477</v>
       </c>
       <c r="F29">
-        <v>3.121</v>
+        <v>3.127</v>
       </c>
       <c r="G29">
-        <v>2.335</v>
+        <v>2.429</v>
       </c>
       <c r="H29">
-        <v>3.907</v>
+        <v>3.826</v>
       </c>
       <c r="I29">
-        <v>2087730.509</v>
+        <v>2126147.293</v>
       </c>
       <c r="J29">
-        <v>1744729.276</v>
+        <v>1809983.41</v>
       </c>
       <c r="K29">
-        <v>2430731.742</v>
+        <v>2442311.176</v>
       </c>
       <c r="L29">
-        <v>415100.532</v>
+        <v>415936.221</v>
       </c>
       <c r="M29">
-        <v>310554.461</v>
+        <v>323012.057</v>
       </c>
       <c r="N29">
-        <v>519646.604</v>
+        <v>508860.386</v>
       </c>
     </row>
     <row r="30">
@@ -1878,40 +1878,40 @@
         </is>
       </c>
       <c r="C32">
-        <v>164.793</v>
+        <v>166.03</v>
       </c>
       <c r="D32">
-        <v>148.951</v>
+        <v>149.76</v>
       </c>
       <c r="E32">
-        <v>180.634</v>
+        <v>182.301</v>
       </c>
       <c r="F32">
-        <v>1341.668</v>
+        <v>1358.658</v>
       </c>
       <c r="G32">
-        <v>1208.009</v>
+        <v>1221.36</v>
       </c>
       <c r="H32">
-        <v>1475.326</v>
+        <v>1495.955</v>
       </c>
       <c r="I32">
-        <v>2774942.564</v>
+        <v>2795785.491</v>
       </c>
       <c r="J32">
-        <v>2508180.947</v>
+        <v>2521800.763</v>
       </c>
       <c r="K32">
-        <v>3041704.181</v>
+        <v>3069770.219</v>
       </c>
       <c r="L32">
-        <v>178441798.194</v>
+        <v>180701473.129</v>
       </c>
       <c r="M32">
-        <v>160665251.876</v>
+        <v>162440900.71</v>
       </c>
       <c r="N32">
-        <v>196218344.512</v>
+        <v>198962045.547</v>
       </c>
     </row>
     <row r="33">
@@ -1926,40 +1926,40 @@
         </is>
       </c>
       <c r="C33">
-        <v>316.368</v>
+        <v>323.128</v>
       </c>
       <c r="D33">
-        <v>288.994</v>
+        <v>295.155</v>
       </c>
       <c r="E33">
-        <v>343.742</v>
+        <v>351.101</v>
       </c>
       <c r="F33">
-        <v>1880.012</v>
+        <v>1934.563</v>
       </c>
       <c r="G33">
-        <v>1712.903</v>
+        <v>1762.18</v>
       </c>
       <c r="H33">
-        <v>2047.121</v>
+        <v>2106.946</v>
       </c>
       <c r="I33">
-        <v>5327318.468</v>
+        <v>5441149.751</v>
       </c>
       <c r="J33">
-        <v>4866362.569</v>
+        <v>4970115.729</v>
       </c>
       <c r="K33">
-        <v>5788274.368</v>
+        <v>5912183.773</v>
       </c>
       <c r="L33">
-        <v>250041604.212</v>
+        <v>257296908.965</v>
       </c>
       <c r="M33">
-        <v>227816066.925</v>
+        <v>234369964.389</v>
       </c>
       <c r="N33">
-        <v>272267141.5</v>
+        <v>280223853.54</v>
       </c>
     </row>
     <row r="34">
@@ -1974,40 +1974,40 @@
         </is>
       </c>
       <c r="C34">
-        <v>1892.446</v>
+        <v>1883.425</v>
       </c>
       <c r="D34">
-        <v>1751.092</v>
+        <v>1742.768</v>
       </c>
       <c r="E34">
-        <v>2033.8</v>
+        <v>2024.082</v>
       </c>
       <c r="F34">
-        <v>7475.846</v>
+        <v>7469.768</v>
       </c>
       <c r="G34">
-        <v>6895.713</v>
+        <v>6890.117</v>
       </c>
       <c r="H34">
-        <v>8055.979</v>
+        <v>8049.419</v>
       </c>
       <c r="I34">
-        <v>31866896.777</v>
+        <v>31714992.267</v>
       </c>
       <c r="J34">
-        <v>29486631.33</v>
+        <v>29346475.367</v>
       </c>
       <c r="K34">
-        <v>34247162.225</v>
+        <v>34083509.166</v>
       </c>
       <c r="L34">
-        <v>994287540.8559999</v>
+        <v>993479155.705</v>
       </c>
       <c r="M34">
-        <v>917129851.142</v>
+        <v>916385556.3660001</v>
       </c>
       <c r="N34">
-        <v>1071445230.569</v>
+        <v>1070572755.044</v>
       </c>
     </row>
     <row r="35">
@@ -2022,40 +2022,40 @@
         </is>
       </c>
       <c r="C35">
-        <v>5140.312</v>
+        <v>5137.655</v>
       </c>
       <c r="D35">
-        <v>4721.506</v>
+        <v>4719.023</v>
       </c>
       <c r="E35">
-        <v>5559.117</v>
+        <v>5556.286</v>
       </c>
       <c r="F35">
-        <v>10420.447</v>
+        <v>10467.159</v>
       </c>
       <c r="G35">
-        <v>9464.362999999999</v>
+        <v>9506.216</v>
       </c>
       <c r="H35">
-        <v>11376.532</v>
+        <v>11428.101</v>
       </c>
       <c r="I35">
-        <v>86557708.49600001</v>
+        <v>86512964.86499999</v>
       </c>
       <c r="J35">
-        <v>79505447.352</v>
+        <v>79463623.02</v>
       </c>
       <c r="K35">
-        <v>93609969.641</v>
+        <v>93562306.70999999</v>
       </c>
       <c r="L35">
-        <v>1385919499.617</v>
+        <v>1392132098.543</v>
       </c>
       <c r="M35">
-        <v>1258760234.384</v>
+        <v>1264326784.468</v>
       </c>
       <c r="N35">
-        <v>1513078764.849</v>
+        <v>1519937412.618</v>
       </c>
     </row>
     <row r="36">
@@ -2070,40 +2070,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>6417.715</v>
+        <v>6434.19</v>
       </c>
       <c r="D36">
-        <v>5668.849</v>
+        <v>5687.267</v>
       </c>
       <c r="E36">
-        <v>7166.581</v>
+        <v>7181.112</v>
       </c>
       <c r="F36">
-        <v>2135.295</v>
+        <v>2136.709</v>
       </c>
       <c r="G36">
-        <v>1739.816</v>
+        <v>1743.054</v>
       </c>
       <c r="H36">
-        <v>2530.774</v>
+        <v>2530.365</v>
       </c>
       <c r="I36">
-        <v>108067906.007</v>
+        <v>108345322.313</v>
       </c>
       <c r="J36">
-        <v>95457747.28300001</v>
+        <v>95767897.31299999</v>
       </c>
       <c r="K36">
-        <v>120678064.732</v>
+        <v>120922747.313</v>
       </c>
       <c r="L36">
-        <v>283994227.076</v>
+        <v>284182333.741</v>
       </c>
       <c r="M36">
-        <v>231395532.494</v>
+        <v>231826132.579</v>
       </c>
       <c r="N36">
-        <v>336592921.659</v>
+        <v>336538534.903</v>
       </c>
     </row>
     <row r="37">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C37">
-        <v>19059.373</v>
+        <v>22273.704</v>
       </c>
       <c r="D37">
-        <v>16678.194</v>
+        <v>19568.395</v>
       </c>
       <c r="E37">
-        <v>21440.553</v>
+        <v>24979.012</v>
       </c>
       <c r="F37">
-        <v>10754.246</v>
+        <v>12326.029</v>
       </c>
       <c r="G37">
-        <v>9323.852999999999</v>
+        <v>10728.074</v>
       </c>
       <c r="H37">
-        <v>12184.638</v>
+        <v>13923.984</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2145,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>1430314694.148</v>
+        <v>1639361839.408</v>
       </c>
       <c r="M37">
-        <v>1240072476.212</v>
+        <v>1426833788.906</v>
       </c>
       <c r="N37">
-        <v>1620556912.083</v>
+        <v>1851889889.909</v>
       </c>
     </row>
     <row r="38">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="C38">
-        <v>20627.366</v>
+        <v>23935.032</v>
       </c>
       <c r="D38">
-        <v>18217.853</v>
+        <v>21190.017</v>
       </c>
       <c r="E38">
-        <v>23036.879</v>
+        <v>26680.047</v>
       </c>
       <c r="F38">
-        <v>9857.593000000001</v>
+        <v>11271.758</v>
       </c>
       <c r="G38">
-        <v>8627.902</v>
+        <v>9887.201999999999</v>
       </c>
       <c r="H38">
-        <v>11087.284</v>
+        <v>12656.313</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2193,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>1311059824.67</v>
+        <v>1499143773.725</v>
       </c>
       <c r="M38">
-        <v>1147510922.221</v>
+        <v>1314997887.285</v>
       </c>
       <c r="N38">
-        <v>1474608727.12</v>
+        <v>1683289660.164</v>
       </c>
     </row>
     <row r="39">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="C39">
-        <v>19804.174</v>
+        <v>22861.429</v>
       </c>
       <c r="D39">
-        <v>17650.574</v>
+        <v>20389.719</v>
       </c>
       <c r="E39">
-        <v>21957.774</v>
+        <v>25333.139</v>
       </c>
       <c r="F39">
-        <v>7833.167</v>
+        <v>8906.635</v>
       </c>
       <c r="G39">
-        <v>6899.255</v>
+        <v>7853.238</v>
       </c>
       <c r="H39">
-        <v>8767.079</v>
+        <v>9960.031000000001</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2241,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>1041811263.848</v>
+        <v>1184582394.841</v>
       </c>
       <c r="M39">
-        <v>917600968.066</v>
+        <v>1044480667.873</v>
       </c>
       <c r="N39">
-        <v>1166021559.629</v>
+        <v>1324684121.808</v>
       </c>
     </row>
     <row r="40">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="C40">
-        <v>19532.838</v>
+        <v>22029.123</v>
       </c>
       <c r="D40">
-        <v>17606.472</v>
+        <v>19863.057</v>
       </c>
       <c r="E40">
-        <v>21459.204</v>
+        <v>24195.188</v>
       </c>
       <c r="F40">
-        <v>5819.533</v>
+        <v>6433.228</v>
       </c>
       <c r="G40">
-        <v>5192.584</v>
+        <v>5743.578</v>
       </c>
       <c r="H40">
-        <v>6446.483</v>
+        <v>7122.878</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>773997952.4220001</v>
+        <v>855619354.455</v>
       </c>
       <c r="M40">
-        <v>690613645.9400001</v>
+        <v>763895877.086</v>
       </c>
       <c r="N40">
-        <v>857382258.904</v>
+        <v>947342831.824</v>
       </c>
     </row>
     <row r="41">
@@ -2310,22 +2310,22 @@
         </is>
       </c>
       <c r="C41">
-        <v>23814.422</v>
+        <v>27174.477</v>
       </c>
       <c r="D41">
-        <v>21819.172</v>
+        <v>24917.933</v>
       </c>
       <c r="E41">
-        <v>25809.672</v>
+        <v>29431.021</v>
       </c>
       <c r="F41">
-        <v>4863.278</v>
+        <v>5439.667</v>
       </c>
       <c r="G41">
-        <v>4410.115</v>
+        <v>4935.977</v>
       </c>
       <c r="H41">
-        <v>5316.441</v>
+        <v>5943.356</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2337,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>646816011.408</v>
+        <v>723475658.411</v>
       </c>
       <c r="M41">
-        <v>586545361.197</v>
+        <v>656484953.552</v>
       </c>
       <c r="N41">
-        <v>707086661.62</v>
+        <v>790466363.27</v>
       </c>
     </row>
     <row r="42">
@@ -2358,22 +2358,22 @@
         </is>
       </c>
       <c r="C42">
-        <v>16054.343</v>
+        <v>17889.948</v>
       </c>
       <c r="D42">
-        <v>14552.917</v>
+        <v>16224.938</v>
       </c>
       <c r="E42">
-        <v>17555.77</v>
+        <v>19554.958</v>
       </c>
       <c r="F42">
-        <v>1769.424</v>
+        <v>1949.516</v>
       </c>
       <c r="G42">
-        <v>1569.03</v>
+        <v>1728.939</v>
       </c>
       <c r="H42">
-        <v>1969.818</v>
+        <v>2170.092</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>235333355.395</v>
+        <v>259285579.977</v>
       </c>
       <c r="M42">
-        <v>208680950.991</v>
+        <v>229948940.24</v>
       </c>
       <c r="N42">
-        <v>261985759.8</v>
+        <v>288622219.714</v>
       </c>
     </row>
     <row r="43">
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="C43">
-        <v>7116.33</v>
+        <v>7836.06</v>
       </c>
       <c r="D43">
-        <v>6183.013</v>
+        <v>6813.559</v>
       </c>
       <c r="E43">
-        <v>8049.646</v>
+        <v>8858.561</v>
       </c>
       <c r="F43">
-        <v>144.073</v>
+        <v>152.736</v>
       </c>
       <c r="G43">
-        <v>114.073</v>
+        <v>121.215</v>
       </c>
       <c r="H43">
-        <v>174.073</v>
+        <v>184.257</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>19161736.984</v>
+        <v>20313886.808</v>
       </c>
       <c r="M43">
-        <v>15171771.786</v>
+        <v>16121609.306</v>
       </c>
       <c r="N43">
-        <v>23151702.182</v>
+        <v>24506164.309</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/HIA_per_age_Rubin.xlsx
+++ b/output/Tables/2019/HIA_per_age_Rubin.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>450.468</v>
+        <v>416.694</v>
       </c>
       <c r="D2">
-        <v>405.626</v>
+        <v>374.583</v>
       </c>
       <c r="E2">
-        <v>495.31</v>
+        <v>458.804</v>
       </c>
       <c r="F2">
-        <v>25762.1</v>
+        <v>23815.663</v>
       </c>
       <c r="G2">
-        <v>23231.785</v>
+        <v>21446.075</v>
       </c>
       <c r="H2">
-        <v>28292.416</v>
+        <v>26185.251</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>3426359308.911</v>
+        <v>3167483202.466</v>
       </c>
       <c r="M2">
-        <v>3089827354.54</v>
+        <v>2852328005.021</v>
       </c>
       <c r="N2">
-        <v>3762891263.282</v>
+        <v>3482638399.911</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>868.513</v>
+        <v>821.626</v>
       </c>
       <c r="D3">
-        <v>791.576</v>
+        <v>746.931</v>
       </c>
       <c r="E3">
-        <v>945.451</v>
+        <v>896.321</v>
       </c>
       <c r="F3">
-        <v>40414.242</v>
+        <v>38186.177</v>
       </c>
       <c r="G3">
-        <v>36939.9</v>
+        <v>34821.773</v>
       </c>
       <c r="H3">
-        <v>43888.583</v>
+        <v>41550.581</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>5375094128.631</v>
+        <v>5078761539.075</v>
       </c>
       <c r="M3">
-        <v>4913006686.786</v>
+        <v>4631295823.924</v>
       </c>
       <c r="N3">
-        <v>5837181570.476</v>
+        <v>5526227254.227</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>2313.768</v>
+        <v>2178.412</v>
       </c>
       <c r="D4">
-        <v>2114.198</v>
+        <v>1985.808</v>
       </c>
       <c r="E4">
-        <v>2513.338</v>
+        <v>2371.016</v>
       </c>
       <c r="F4">
-        <v>85887.20600000001</v>
+        <v>80874.758</v>
       </c>
       <c r="G4">
-        <v>78647.952</v>
+        <v>73885.235</v>
       </c>
       <c r="H4">
-        <v>93126.461</v>
+        <v>87864.281</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>11422998462.233</v>
+        <v>10756342834.79</v>
       </c>
       <c r="M4">
-        <v>10460177628.167</v>
+        <v>9826736238.702</v>
       </c>
       <c r="N4">
-        <v>12385819296.3</v>
+        <v>11685949430.878</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>4889.279</v>
+        <v>4571.617</v>
       </c>
       <c r="D5">
-        <v>4510.361</v>
+        <v>4206.035</v>
       </c>
       <c r="E5">
-        <v>5268.197</v>
+        <v>4937.199</v>
       </c>
       <c r="F5">
-        <v>131630.88</v>
+        <v>122804.905</v>
       </c>
       <c r="G5">
-        <v>121863.918</v>
+        <v>113404.777</v>
       </c>
       <c r="H5">
-        <v>141397.843</v>
+        <v>132205.032</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>17506907073.951</v>
+        <v>16333052320.801</v>
       </c>
       <c r="M5">
-        <v>16207901049.258</v>
+        <v>15082835384.6</v>
       </c>
       <c r="N5">
-        <v>18805913098.645</v>
+        <v>17583269257.001</v>
       </c>
     </row>
     <row r="6">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C6">
-        <v>10474.488</v>
+        <v>9456.378000000001</v>
       </c>
       <c r="D6">
-        <v>9700.778</v>
+        <v>8722.610000000001</v>
       </c>
       <c r="E6">
-        <v>11248.198</v>
+        <v>10190.147</v>
       </c>
       <c r="F6">
-        <v>178798.114</v>
+        <v>161442.839</v>
       </c>
       <c r="G6">
-        <v>166201.989</v>
+        <v>149436.165</v>
       </c>
       <c r="H6">
-        <v>191394.239</v>
+        <v>173449.512</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>23780149184.565</v>
+        <v>21471897522.77</v>
       </c>
       <c r="M6">
-        <v>22104864547.14</v>
+        <v>19875009912.393</v>
       </c>
       <c r="N6">
-        <v>25455433821.989</v>
+        <v>23068785133.147</v>
       </c>
     </row>
     <row r="7">
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>16764.82</v>
+        <v>14836.235</v>
       </c>
       <c r="D7">
-        <v>15377.286</v>
+        <v>13517.703</v>
       </c>
       <c r="E7">
-        <v>18152.354</v>
+        <v>16154.767</v>
       </c>
       <c r="F7">
-        <v>124329.441</v>
+        <v>108618.568</v>
       </c>
       <c r="G7">
-        <v>115284.935</v>
+        <v>100234.845</v>
       </c>
       <c r="H7">
-        <v>133373.946</v>
+        <v>117002.291</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>16535815601.577</v>
+        <v>14446269580.715</v>
       </c>
       <c r="M7">
-        <v>15332896321.082</v>
+        <v>13331234403.495</v>
       </c>
       <c r="N7">
-        <v>17738734882.073</v>
+        <v>15561304757.934</v>
       </c>
     </row>
     <row r="8">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>23163.833</v>
+        <v>19077.981</v>
       </c>
       <c r="D8">
-        <v>20583.601</v>
+        <v>16804.034</v>
       </c>
       <c r="E8">
-        <v>25744.066</v>
+        <v>21351.928</v>
       </c>
       <c r="F8">
-        <v>20137.822</v>
+        <v>16594.887</v>
       </c>
       <c r="G8">
-        <v>17030.804</v>
+        <v>13803.6</v>
       </c>
       <c r="H8">
-        <v>23244.84</v>
+        <v>19386.175</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>2678330275.687</v>
+        <v>2207120036.826</v>
       </c>
       <c r="M8">
-        <v>2265096879.666</v>
+        <v>1835878837.349</v>
       </c>
       <c r="N8">
-        <v>3091563671.709</v>
+        <v>2578361236.303</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>234.716</v>
+        <v>212.993</v>
       </c>
       <c r="D9">
-        <v>209.214</v>
+        <v>189.483</v>
       </c>
       <c r="E9">
-        <v>260.218</v>
+        <v>236.502</v>
       </c>
       <c r="F9">
-        <v>886.468</v>
+        <v>470.29</v>
       </c>
       <c r="G9">
-        <v>789.725</v>
+        <v>420.408</v>
       </c>
       <c r="H9">
-        <v>983.21</v>
+        <v>520.172</v>
       </c>
       <c r="I9">
-        <v>13074137.71</v>
+        <v>11223641.93</v>
       </c>
       <c r="J9">
-        <v>11653620.506</v>
+        <v>9984799.414000001</v>
       </c>
       <c r="K9">
-        <v>14494654.913</v>
+        <v>12462484.447</v>
       </c>
       <c r="L9">
-        <v>117900187.086</v>
+        <v>62548613.07</v>
       </c>
       <c r="M9">
-        <v>105033379.758</v>
+        <v>55914300.855</v>
       </c>
       <c r="N9">
-        <v>130766994.415</v>
+        <v>69182925.285</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>490.129</v>
+        <v>452.518</v>
       </c>
       <c r="D10">
-        <v>442.671</v>
+        <v>407.034</v>
       </c>
       <c r="E10">
-        <v>537.588</v>
+        <v>498.003</v>
       </c>
       <c r="F10">
-        <v>1524.596</v>
+        <v>1150.568</v>
       </c>
       <c r="G10">
-        <v>1376.936</v>
+        <v>1037.301</v>
       </c>
       <c r="H10">
-        <v>1672.256</v>
+        <v>1263.834</v>
       </c>
       <c r="I10">
-        <v>27301181.399</v>
+        <v>23845436.656</v>
       </c>
       <c r="J10">
-        <v>24657649.238</v>
+        <v>21448630.85</v>
       </c>
       <c r="K10">
-        <v>29944713.561</v>
+        <v>26242242.461</v>
       </c>
       <c r="L10">
-        <v>202771277.687</v>
+        <v>153025507.498</v>
       </c>
       <c r="M10">
-        <v>183132512.063</v>
+        <v>137961034.207</v>
       </c>
       <c r="N10">
-        <v>222410043.31</v>
+        <v>168089980.788</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1696.728</v>
+        <v>1577.237</v>
       </c>
       <c r="D11">
-        <v>1526.361</v>
+        <v>1413.298</v>
       </c>
       <c r="E11">
-        <v>1867.096</v>
+        <v>1741.176</v>
       </c>
       <c r="F11">
-        <v>4221.09</v>
+        <v>3525.974</v>
       </c>
       <c r="G11">
-        <v>3793.413</v>
+        <v>3168.994</v>
       </c>
       <c r="H11">
-        <v>4648.767</v>
+        <v>3882.954</v>
       </c>
       <c r="I11">
-        <v>94511166.69599999</v>
+        <v>83112498.243</v>
       </c>
       <c r="J11">
-        <v>85021366.551</v>
+        <v>74473740.324</v>
       </c>
       <c r="K11">
-        <v>104000966.841</v>
+        <v>91751256.161</v>
       </c>
       <c r="L11">
-        <v>561404922.712</v>
+        <v>468954510.513</v>
       </c>
       <c r="M11">
-        <v>504523894.08</v>
+        <v>421476139.009</v>
       </c>
       <c r="N11">
-        <v>618285951.344</v>
+        <v>516432882.018</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>3880.736</v>
+        <v>3555.54</v>
       </c>
       <c r="D12">
-        <v>3548.037</v>
+        <v>3238.894</v>
       </c>
       <c r="E12">
-        <v>4213.435</v>
+        <v>3872.187</v>
       </c>
       <c r="F12">
-        <v>6986.253</v>
+        <v>6774.943</v>
       </c>
       <c r="G12">
-        <v>6390.645</v>
+        <v>6182.107</v>
       </c>
       <c r="H12">
-        <v>7581.861</v>
+        <v>7367.779</v>
       </c>
       <c r="I12">
-        <v>216164754.847</v>
+        <v>187359192.016</v>
       </c>
       <c r="J12">
-        <v>197632738.267</v>
+        <v>170673511.729</v>
       </c>
       <c r="K12">
-        <v>234696771.428</v>
+        <v>204044872.302</v>
       </c>
       <c r="L12">
-        <v>929171620.182</v>
+        <v>901067440.79</v>
       </c>
       <c r="M12">
-        <v>849955775.275</v>
+        <v>822220226.477</v>
       </c>
       <c r="N12">
-        <v>1008387465.09</v>
+        <v>979914655.103</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>11712.422</v>
+        <v>10339.618</v>
       </c>
       <c r="D13">
-        <v>10769.859</v>
+        <v>9436.412</v>
       </c>
       <c r="E13">
-        <v>12654.984</v>
+        <v>11242.825</v>
       </c>
       <c r="F13">
-        <v>13862.475</v>
+        <v>14438.318</v>
       </c>
       <c r="G13">
-        <v>12737.3</v>
+        <v>13196.21</v>
       </c>
       <c r="H13">
-        <v>14987.65</v>
+        <v>15680.425</v>
       </c>
       <c r="I13">
-        <v>652405304.904</v>
+        <v>544846183.574</v>
       </c>
       <c r="J13">
-        <v>599902667.47</v>
+        <v>497251709.403</v>
       </c>
       <c r="K13">
-        <v>704907942.3380001</v>
+        <v>592440657.745</v>
       </c>
       <c r="L13">
-        <v>1843709199.381</v>
+        <v>1920296263.671</v>
       </c>
       <c r="M13">
-        <v>1694060914.898</v>
+        <v>1755095989.912</v>
       </c>
       <c r="N13">
-        <v>1993357483.864</v>
+        <v>2085496537.431</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>13598.257</v>
+        <v>11751.079</v>
       </c>
       <c r="D14">
-        <v>12460.343</v>
+        <v>10683.699</v>
       </c>
       <c r="E14">
-        <v>14736.171</v>
+        <v>12818.459</v>
       </c>
       <c r="F14">
-        <v>8004.189</v>
+        <v>14494.055</v>
       </c>
       <c r="G14">
-        <v>7292.748</v>
+        <v>13163.114</v>
       </c>
       <c r="H14">
-        <v>8715.629999999999</v>
+        <v>15824.997</v>
       </c>
       <c r="I14">
-        <v>757450121.765</v>
+        <v>619223104.851</v>
       </c>
       <c r="J14">
-        <v>694066047.489</v>
+        <v>562977497.993</v>
       </c>
       <c r="K14">
-        <v>820834196.0420001</v>
+        <v>675468711.709</v>
       </c>
       <c r="L14">
-        <v>1064557138.908</v>
+        <v>1927709366.686</v>
       </c>
       <c r="M14">
-        <v>969935431.303</v>
+        <v>1750694190.725</v>
       </c>
       <c r="N14">
-        <v>1159178846.513</v>
+        <v>2104724542.647</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>9078.575000000001</v>
+        <v>7379.313</v>
       </c>
       <c r="D15">
-        <v>7983.545</v>
+        <v>6391.727</v>
       </c>
       <c r="E15">
-        <v>10173.604</v>
+        <v>8366.9</v>
       </c>
       <c r="F15">
-        <v>807.12</v>
+        <v>7798.337</v>
       </c>
       <c r="G15">
-        <v>656.401</v>
+        <v>6743.358</v>
       </c>
       <c r="H15">
-        <v>957.8390000000001</v>
+        <v>8853.315000000001</v>
       </c>
       <c r="I15">
-        <v>505694777.718</v>
+        <v>388852918.16</v>
       </c>
       <c r="J15">
-        <v>444699443.631</v>
+        <v>336812066.605</v>
       </c>
       <c r="K15">
-        <v>566690111.804</v>
+        <v>440893769.715</v>
       </c>
       <c r="L15">
-        <v>107346957.88</v>
+        <v>1037178789.239</v>
       </c>
       <c r="M15">
-        <v>87301277.20100001</v>
+        <v>896866655.036</v>
       </c>
       <c r="N15">
-        <v>127392638.559</v>
+        <v>1177490923.442</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>1874.359</v>
+        <v>77.02200000000001</v>
       </c>
       <c r="D16">
-        <v>1584.59</v>
+        <v>67.01300000000001</v>
       </c>
       <c r="E16">
-        <v>2164.129</v>
+        <v>87.03100000000001</v>
       </c>
       <c r="F16">
-        <v>6327.123</v>
+        <v>46.95</v>
       </c>
       <c r="G16">
-        <v>5324.072</v>
+        <v>40.765</v>
       </c>
       <c r="H16">
-        <v>7330.173</v>
+        <v>53.135</v>
       </c>
       <c r="I16">
-        <v>27753639.176</v>
+        <v>2258211.685</v>
       </c>
       <c r="J16">
-        <v>23463018.138</v>
+        <v>1964757.134</v>
       </c>
       <c r="K16">
-        <v>32044260.213</v>
+        <v>2551666.237</v>
       </c>
       <c r="L16">
-        <v>841507329.159</v>
+        <v>6244303.469</v>
       </c>
       <c r="M16">
-        <v>708101585.302</v>
+        <v>5421711.973</v>
       </c>
       <c r="N16">
-        <v>974913073.016</v>
+        <v>7066894.965</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>3207.574</v>
+        <v>234.192</v>
       </c>
       <c r="D17">
-        <v>2741.753</v>
+        <v>204.731</v>
       </c>
       <c r="E17">
-        <v>3673.395</v>
+        <v>263.653</v>
       </c>
       <c r="F17">
-        <v>9088.564</v>
+        <v>140.224</v>
       </c>
       <c r="G17">
-        <v>7735.067</v>
+        <v>122.362</v>
       </c>
       <c r="H17">
-        <v>10442.061</v>
+        <v>158.085</v>
       </c>
       <c r="I17">
-        <v>47494548.472</v>
+        <v>6866272.156</v>
       </c>
       <c r="J17">
-        <v>40597134.325</v>
+        <v>6002499.365</v>
       </c>
       <c r="K17">
-        <v>54391962.619</v>
+        <v>7730044.948</v>
       </c>
       <c r="L17">
-        <v>1208779033.84</v>
+        <v>18649776.322</v>
       </c>
       <c r="M17">
-        <v>1028763909.844</v>
+        <v>16274197.951</v>
       </c>
       <c r="N17">
-        <v>1388794157.836</v>
+        <v>21025354.692</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>4263.157</v>
+        <v>563.615</v>
       </c>
       <c r="D18">
-        <v>3704.202</v>
+        <v>494.217</v>
       </c>
       <c r="E18">
-        <v>4822.111</v>
+        <v>633.014</v>
       </c>
       <c r="F18">
-        <v>9720.277</v>
+        <v>316.338</v>
       </c>
       <c r="G18">
-        <v>8379.331</v>
+        <v>276.195</v>
       </c>
       <c r="H18">
-        <v>11061.224</v>
+        <v>356.481</v>
       </c>
       <c r="I18">
-        <v>63124562.685</v>
+        <v>16524637.548</v>
       </c>
       <c r="J18">
-        <v>54848122.829</v>
+        <v>14489937.439</v>
       </c>
       <c r="K18">
-        <v>71401002.54099999</v>
+        <v>18559337.656</v>
       </c>
       <c r="L18">
-        <v>1292796899.266</v>
+        <v>42072962.405</v>
       </c>
       <c r="M18">
-        <v>1114450982.353</v>
+        <v>36733963.451</v>
       </c>
       <c r="N18">
-        <v>1471142816.178</v>
+        <v>47411961.359</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>5446.525</v>
+        <v>1120.788</v>
       </c>
       <c r="D19">
-        <v>4836.711</v>
+        <v>1000.704</v>
       </c>
       <c r="E19">
-        <v>6056.338</v>
+        <v>1240.873</v>
       </c>
       <c r="F19">
-        <v>8945.675999999999</v>
+        <v>583.546</v>
       </c>
       <c r="G19">
-        <v>7899.928</v>
+        <v>519.755</v>
       </c>
       <c r="H19">
-        <v>9991.424999999999</v>
+        <v>647.337</v>
       </c>
       <c r="I19">
-        <v>80646694.008</v>
+        <v>32860394.878</v>
       </c>
       <c r="J19">
-        <v>71617185.62800001</v>
+        <v>29339647.785</v>
       </c>
       <c r="K19">
-        <v>89676202.389</v>
+        <v>36381141.972</v>
       </c>
       <c r="L19">
-        <v>1189774930.996</v>
+        <v>77611616.046</v>
       </c>
       <c r="M19">
-        <v>1050690396.01</v>
+        <v>69127472.557</v>
       </c>
       <c r="N19">
-        <v>1328859465.981</v>
+        <v>86095759.536</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>8069.412</v>
+        <v>2598.416</v>
       </c>
       <c r="D20">
-        <v>7311.197</v>
+        <v>2311.226</v>
       </c>
       <c r="E20">
-        <v>8827.627</v>
+        <v>2885.606</v>
       </c>
       <c r="F20">
-        <v>8587.796</v>
+        <v>1275.506</v>
       </c>
       <c r="G20">
-        <v>7751.862</v>
+        <v>1139.952</v>
       </c>
       <c r="H20">
-        <v>9423.73</v>
+        <v>1411.06</v>
       </c>
       <c r="I20">
-        <v>119483787.571</v>
+        <v>76182957.55400001</v>
       </c>
       <c r="J20">
-        <v>108256894.886</v>
+        <v>67762823.705</v>
       </c>
       <c r="K20">
-        <v>130710680.256</v>
+        <v>84603091.404</v>
       </c>
       <c r="L20">
-        <v>1142176891.101</v>
+        <v>169642357.55</v>
       </c>
       <c r="M20">
-        <v>1030997651.373</v>
+        <v>151613669.07</v>
       </c>
       <c r="N20">
-        <v>1253356130.83</v>
+        <v>187671046.031</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>5268.879</v>
+        <v>2406.577</v>
       </c>
       <c r="D21">
-        <v>4712.767</v>
+        <v>2114.816</v>
       </c>
       <c r="E21">
-        <v>5824.99</v>
+        <v>2698.338</v>
       </c>
       <c r="F21">
-        <v>2671.474</v>
+        <v>1085.091</v>
       </c>
       <c r="G21">
-        <v>2373.559</v>
+        <v>957.048</v>
       </c>
       <c r="H21">
-        <v>2969.388</v>
+        <v>1213.134</v>
       </c>
       <c r="I21">
-        <v>78016287.76100001</v>
+        <v>70558427.788</v>
       </c>
       <c r="J21">
-        <v>69781944.177</v>
+        <v>62004294.713</v>
       </c>
       <c r="K21">
-        <v>86250631.346</v>
+        <v>79112560.86300001</v>
       </c>
       <c r="L21">
-        <v>355305978.865</v>
+        <v>144317100.163</v>
       </c>
       <c r="M21">
-        <v>315683309.65</v>
+        <v>127287413.882</v>
       </c>
       <c r="N21">
-        <v>394928648.081</v>
+        <v>161346786.443</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>2099.613</v>
+        <v>1197.461</v>
       </c>
       <c r="D22">
-        <v>1753.642</v>
+        <v>970.0069999999999</v>
       </c>
       <c r="E22">
-        <v>2445.584</v>
+        <v>1424.915</v>
       </c>
       <c r="F22">
-        <v>137.601</v>
+        <v>411.077</v>
       </c>
       <c r="G22">
-        <v>107.192</v>
+        <v>336.112</v>
       </c>
       <c r="H22">
-        <v>168.01</v>
+        <v>486.042</v>
       </c>
       <c r="I22">
-        <v>31088975.147</v>
+        <v>35108357.865</v>
       </c>
       <c r="J22">
-        <v>25966182.995</v>
+        <v>28439627.059</v>
       </c>
       <c r="K22">
-        <v>36211767.299</v>
+        <v>41777088.67</v>
       </c>
       <c r="L22">
-        <v>18300883.25</v>
+        <v>54673271.315</v>
       </c>
       <c r="M22">
-        <v>14256491.16</v>
+        <v>44702917.234</v>
       </c>
       <c r="N22">
-        <v>22345275.341</v>
+        <v>64643625.397</v>
       </c>
     </row>
     <row r="23">
@@ -1446,40 +1446,40 @@
         </is>
       </c>
       <c r="C23">
-        <v>406.088</v>
+        <v>364.537</v>
       </c>
       <c r="D23">
-        <v>354.034</v>
+        <v>317.11</v>
       </c>
       <c r="E23">
-        <v>458.141</v>
+        <v>411.965</v>
       </c>
       <c r="F23">
-        <v>1634.356</v>
+        <v>201.687</v>
       </c>
       <c r="G23">
-        <v>1421.893</v>
+        <v>175.115</v>
       </c>
       <c r="H23">
-        <v>1846.819</v>
+        <v>228.259</v>
       </c>
       <c r="I23">
-        <v>30538206.47</v>
+        <v>14290224.722</v>
       </c>
       <c r="J23">
-        <v>26623732.802</v>
+        <v>12431013.27</v>
       </c>
       <c r="K23">
-        <v>34452680.138</v>
+        <v>16149436.175</v>
       </c>
       <c r="L23">
-        <v>217369361.393</v>
+        <v>26824379.016</v>
       </c>
       <c r="M23">
-        <v>189111819.54</v>
+        <v>23290271.892</v>
       </c>
       <c r="N23">
-        <v>245626903.246</v>
+        <v>30358486.139</v>
       </c>
     </row>
     <row r="24">
@@ -1494,40 +1494,40 @@
         </is>
       </c>
       <c r="C24">
-        <v>658.669</v>
+        <v>597.424</v>
       </c>
       <c r="D24">
-        <v>580.042</v>
+        <v>522.822</v>
       </c>
       <c r="E24">
-        <v>737.297</v>
+        <v>672.026</v>
       </c>
       <c r="F24">
-        <v>2186.06</v>
+        <v>577.946</v>
       </c>
       <c r="G24">
-        <v>1921.615</v>
+        <v>505.214</v>
       </c>
       <c r="H24">
-        <v>2450.504</v>
+        <v>650.677</v>
       </c>
       <c r="I24">
-        <v>49532595.314</v>
+        <v>23419635.258</v>
       </c>
       <c r="J24">
-        <v>43619754.883</v>
+        <v>20495160.09</v>
       </c>
       <c r="K24">
-        <v>55445435.745</v>
+        <v>26344110.426</v>
       </c>
       <c r="L24">
-        <v>290745914.382</v>
+        <v>76866776.441</v>
       </c>
       <c r="M24">
-        <v>255574793.163</v>
+        <v>67193474.289</v>
       </c>
       <c r="N24">
-        <v>325917035.601</v>
+        <v>86540078.594</v>
       </c>
     </row>
     <row r="25">
@@ -1542,40 +1542,40 @@
         </is>
       </c>
       <c r="C25">
-        <v>983.914</v>
+        <v>892.063</v>
       </c>
       <c r="D25">
-        <v>864.652</v>
+        <v>779.612</v>
       </c>
       <c r="E25">
-        <v>1103.176</v>
+        <v>1004.514</v>
       </c>
       <c r="F25">
-        <v>2597.435</v>
+        <v>1127.976</v>
       </c>
       <c r="G25">
-        <v>2278.214</v>
+        <v>985.046</v>
       </c>
       <c r="H25">
-        <v>2916.655</v>
+        <v>1270.906</v>
       </c>
       <c r="I25">
-        <v>73991305.87800001</v>
+        <v>34969761.264</v>
       </c>
       <c r="J25">
-        <v>65022695.461</v>
+        <v>30561559.26</v>
       </c>
       <c r="K25">
-        <v>82959916.296</v>
+        <v>39377963.268</v>
       </c>
       <c r="L25">
-        <v>345458847.18</v>
+        <v>150020831.753</v>
       </c>
       <c r="M25">
-        <v>303002517.959</v>
+        <v>131011156.98</v>
       </c>
       <c r="N25">
-        <v>387915176.402</v>
+        <v>169030506.525</v>
       </c>
     </row>
     <row r="26">
@@ -1590,40 +1590,40 @@
         </is>
       </c>
       <c r="C26">
-        <v>1514.552</v>
+        <v>1379.693</v>
       </c>
       <c r="D26">
-        <v>1361.019</v>
+        <v>1234.495</v>
       </c>
       <c r="E26">
-        <v>1668.085</v>
+        <v>1524.891</v>
       </c>
       <c r="F26">
-        <v>2922.042</v>
+        <v>1703.237</v>
       </c>
       <c r="G26">
-        <v>2623.041</v>
+        <v>1518.109</v>
       </c>
       <c r="H26">
-        <v>3221.044</v>
+        <v>1888.365</v>
       </c>
       <c r="I26">
-        <v>113895818.304</v>
+        <v>54085347.004</v>
       </c>
       <c r="J26">
-        <v>102349979.01</v>
+        <v>48393428.655</v>
       </c>
       <c r="K26">
-        <v>125441657.598</v>
+        <v>59777265.353</v>
       </c>
       <c r="L26">
-        <v>388631629.378</v>
+        <v>226530525.939</v>
       </c>
       <c r="M26">
-        <v>348864447.404</v>
+        <v>201908505.11</v>
       </c>
       <c r="N26">
-        <v>428398811.353</v>
+        <v>251152546.769</v>
       </c>
     </row>
     <row r="27">
@@ -1638,40 +1638,40 @@
         </is>
       </c>
       <c r="C27">
-        <v>2178.529</v>
+        <v>1900.157</v>
       </c>
       <c r="D27">
-        <v>1978.309</v>
+        <v>1710.516</v>
       </c>
       <c r="E27">
-        <v>2378.749</v>
+        <v>2089.797</v>
       </c>
       <c r="F27">
-        <v>2807.034</v>
+        <v>3212.594</v>
       </c>
       <c r="G27">
-        <v>2543.399</v>
+        <v>2866.83</v>
       </c>
       <c r="H27">
-        <v>3070.67</v>
+        <v>3558.357</v>
       </c>
       <c r="I27">
-        <v>163827582.305</v>
+        <v>74488048.037</v>
       </c>
       <c r="J27">
-        <v>148770838.926</v>
+        <v>67053948.59</v>
       </c>
       <c r="K27">
-        <v>178884325.684</v>
+        <v>81922147.484</v>
       </c>
       <c r="L27">
-        <v>373335563.358</v>
+        <v>427274966.141</v>
       </c>
       <c r="M27">
-        <v>338272022.669</v>
+        <v>381288402.599</v>
       </c>
       <c r="N27">
-        <v>408399104.048</v>
+        <v>473261529.684</v>
       </c>
     </row>
     <row r="28">
@@ -1686,40 +1686,40 @@
         </is>
       </c>
       <c r="C28">
-        <v>697.8440000000001</v>
+        <v>597.341</v>
       </c>
       <c r="D28">
-        <v>627.596</v>
+        <v>531.078</v>
       </c>
       <c r="E28">
-        <v>768.092</v>
+        <v>663.604</v>
       </c>
       <c r="F28">
-        <v>458.924</v>
+        <v>2524.107</v>
       </c>
       <c r="G28">
-        <v>408.148</v>
+        <v>2219.429</v>
       </c>
       <c r="H28">
-        <v>509.701</v>
+        <v>2828.785</v>
       </c>
       <c r="I28">
-        <v>52478563.195</v>
+        <v>23416379.941</v>
       </c>
       <c r="J28">
-        <v>47195833.937</v>
+        <v>20818802.522</v>
       </c>
       <c r="K28">
-        <v>57761292.452</v>
+        <v>26013957.36</v>
       </c>
       <c r="L28">
-        <v>61036936.274</v>
+        <v>335706237.489</v>
       </c>
       <c r="M28">
-        <v>54283664.185</v>
+        <v>295184064.479</v>
       </c>
       <c r="N28">
-        <v>67790208.36300001</v>
+        <v>376228410.499</v>
       </c>
     </row>
     <row r="29">
@@ -1734,40 +1734,40 @@
         </is>
       </c>
       <c r="C29">
-        <v>28.273</v>
+        <v>22.826</v>
       </c>
       <c r="D29">
-        <v>24.069</v>
+        <v>18.936</v>
       </c>
       <c r="E29">
-        <v>32.477</v>
+        <v>26.716</v>
       </c>
       <c r="F29">
-        <v>3.127</v>
+        <v>1008.818</v>
       </c>
       <c r="G29">
-        <v>2.429</v>
+        <v>811.853</v>
       </c>
       <c r="H29">
-        <v>3.826</v>
+        <v>1205.782</v>
       </c>
       <c r="I29">
-        <v>2126147.293</v>
+        <v>894806.934</v>
       </c>
       <c r="J29">
-        <v>1809983.41</v>
+        <v>742325.977</v>
       </c>
       <c r="K29">
-        <v>2442311.176</v>
+        <v>1047287.891</v>
       </c>
       <c r="L29">
-        <v>415936.221</v>
+        <v>134172763.135</v>
       </c>
       <c r="M29">
-        <v>323012.057</v>
+        <v>107976460.155</v>
       </c>
       <c r="N29">
-        <v>508860.386</v>
+        <v>160369066.116</v>
       </c>
     </row>
     <row r="30">
@@ -1878,40 +1878,40 @@
         </is>
       </c>
       <c r="C32">
-        <v>166.03</v>
+        <v>154.693</v>
       </c>
       <c r="D32">
-        <v>149.76</v>
+        <v>138.921</v>
       </c>
       <c r="E32">
-        <v>182.301</v>
+        <v>170.466</v>
       </c>
       <c r="F32">
-        <v>1358.658</v>
+        <v>112.485</v>
       </c>
       <c r="G32">
-        <v>1221.36</v>
+        <v>100.933</v>
       </c>
       <c r="H32">
-        <v>1495.955</v>
+        <v>124.037</v>
       </c>
       <c r="I32">
-        <v>2795785.491</v>
+        <v>2575335.355</v>
       </c>
       <c r="J32">
-        <v>2521800.763</v>
+        <v>2312760.963</v>
       </c>
       <c r="K32">
-        <v>3069770.219</v>
+        <v>2837909.747</v>
       </c>
       <c r="L32">
-        <v>180701473.129</v>
+        <v>14960511.385</v>
       </c>
       <c r="M32">
-        <v>162440900.71</v>
+        <v>13424120.243</v>
       </c>
       <c r="N32">
-        <v>198962045.547</v>
+        <v>16496902.527</v>
       </c>
     </row>
     <row r="33">
@@ -1926,40 +1926,40 @@
         </is>
       </c>
       <c r="C33">
-        <v>323.128</v>
+        <v>288.488</v>
       </c>
       <c r="D33">
-        <v>295.155</v>
+        <v>262.709</v>
       </c>
       <c r="E33">
-        <v>351.101</v>
+        <v>314.267</v>
       </c>
       <c r="F33">
-        <v>1934.563</v>
+        <v>502.017</v>
       </c>
       <c r="G33">
-        <v>1762.18</v>
+        <v>456.4</v>
       </c>
       <c r="H33">
-        <v>2106.946</v>
+        <v>547.635</v>
       </c>
       <c r="I33">
-        <v>5441149.751</v>
+        <v>4802752.289</v>
       </c>
       <c r="J33">
-        <v>4970115.729</v>
+        <v>4373582.785</v>
       </c>
       <c r="K33">
-        <v>5912183.773</v>
+        <v>5231921.792</v>
       </c>
       <c r="L33">
-        <v>257296908.965</v>
+        <v>66768311.413</v>
       </c>
       <c r="M33">
-        <v>234369964.389</v>
+        <v>60701145.026</v>
       </c>
       <c r="N33">
-        <v>280223853.54</v>
+        <v>72835477.801</v>
       </c>
     </row>
     <row r="34">
@@ -1974,40 +1974,40 @@
         </is>
       </c>
       <c r="C34">
-        <v>1883.425</v>
+        <v>1667.51</v>
       </c>
       <c r="D34">
-        <v>1742.768</v>
+        <v>1534.03</v>
       </c>
       <c r="E34">
-        <v>2024.082</v>
+        <v>1800.989</v>
       </c>
       <c r="F34">
-        <v>7469.768</v>
+        <v>1765.375</v>
       </c>
       <c r="G34">
-        <v>6890.117</v>
+        <v>1623.327</v>
       </c>
       <c r="H34">
-        <v>8049.419</v>
+        <v>1907.422</v>
       </c>
       <c r="I34">
-        <v>31714992.267</v>
+        <v>27760699.011</v>
       </c>
       <c r="J34">
-        <v>29346475.367</v>
+        <v>25538538.081</v>
       </c>
       <c r="K34">
-        <v>34083509.166</v>
+        <v>29982859.942</v>
       </c>
       <c r="L34">
-        <v>993479155.705</v>
+        <v>234794857.623</v>
       </c>
       <c r="M34">
-        <v>916385556.3660001</v>
+        <v>215902547.357</v>
       </c>
       <c r="N34">
-        <v>1070572755.044</v>
+        <v>253687167.889</v>
       </c>
     </row>
     <row r="35">
@@ -2022,40 +2022,40 @@
         </is>
       </c>
       <c r="C35">
-        <v>5137.655</v>
+        <v>4373.667</v>
       </c>
       <c r="D35">
-        <v>4719.023</v>
+        <v>3990.67</v>
       </c>
       <c r="E35">
-        <v>5556.286</v>
+        <v>4756.665</v>
       </c>
       <c r="F35">
-        <v>10467.159</v>
+        <v>4846.172</v>
       </c>
       <c r="G35">
-        <v>9506.216</v>
+        <v>4417.383</v>
       </c>
       <c r="H35">
-        <v>11428.101</v>
+        <v>5274.961</v>
       </c>
       <c r="I35">
-        <v>86512964.86499999</v>
+        <v>72812814.517</v>
       </c>
       <c r="J35">
-        <v>79463623.02</v>
+        <v>66436669.71</v>
       </c>
       <c r="K35">
-        <v>93562306.70999999</v>
+        <v>79188959.324</v>
       </c>
       <c r="L35">
-        <v>1392132098.543</v>
+        <v>644540850.796</v>
       </c>
       <c r="M35">
-        <v>1264326784.468</v>
+        <v>587511920.776</v>
       </c>
       <c r="N35">
-        <v>1519937412.618</v>
+        <v>701569780.8150001</v>
       </c>
     </row>
     <row r="36">
@@ -2070,40 +2070,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>6434.19</v>
+        <v>5194.808</v>
       </c>
       <c r="D36">
-        <v>5687.267</v>
+        <v>4523.486</v>
       </c>
       <c r="E36">
-        <v>7181.112</v>
+        <v>5866.129</v>
       </c>
       <c r="F36">
-        <v>2136.709</v>
+        <v>6086.233</v>
       </c>
       <c r="G36">
-        <v>1743.054</v>
+        <v>5293.587</v>
       </c>
       <c r="H36">
-        <v>2530.365</v>
+        <v>6878.88</v>
       </c>
       <c r="I36">
-        <v>108345322.313</v>
+        <v>86483162.598</v>
       </c>
       <c r="J36">
-        <v>95767897.31299999</v>
+        <v>75307001.35600001</v>
       </c>
       <c r="K36">
-        <v>120922747.313</v>
+        <v>97659323.84100001</v>
       </c>
       <c r="L36">
-        <v>284182333.741</v>
+        <v>809469043.38</v>
       </c>
       <c r="M36">
-        <v>231826132.579</v>
+        <v>704047007.9680001</v>
       </c>
       <c r="N36">
-        <v>336538534.903</v>
+        <v>914891078.7920001</v>
       </c>
     </row>
     <row r="37">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C37">
-        <v>22273.704</v>
+        <v>19773.269</v>
       </c>
       <c r="D37">
-        <v>19568.395</v>
+        <v>17454.904</v>
       </c>
       <c r="E37">
-        <v>24979.012</v>
+        <v>22091.634</v>
       </c>
       <c r="F37">
-        <v>12326.029</v>
+        <v>12729.196</v>
       </c>
       <c r="G37">
-        <v>10728.074</v>
+        <v>11196.058</v>
       </c>
       <c r="H37">
-        <v>13923.984</v>
+        <v>14262.334</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2145,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>1639361839.408</v>
+        <v>1692983064.007</v>
       </c>
       <c r="M37">
-        <v>1426833788.906</v>
+        <v>1489075699.745</v>
       </c>
       <c r="N37">
-        <v>1851889889.909</v>
+        <v>1896890428.268</v>
       </c>
     </row>
     <row r="38">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="C38">
-        <v>23935.032</v>
+        <v>21332.001</v>
       </c>
       <c r="D38">
-        <v>21190.017</v>
+        <v>18817.688</v>
       </c>
       <c r="E38">
-        <v>26680.047</v>
+        <v>23846.313</v>
       </c>
       <c r="F38">
-        <v>11271.758</v>
+        <v>11628.331</v>
       </c>
       <c r="G38">
-        <v>9887.201999999999</v>
+        <v>10212.922</v>
       </c>
       <c r="H38">
-        <v>12656.313</v>
+        <v>13043.74</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2193,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>1499143773.725</v>
+        <v>1546568027.858</v>
       </c>
       <c r="M38">
-        <v>1314997887.285</v>
+        <v>1358318659.807</v>
       </c>
       <c r="N38">
-        <v>1683289660.164</v>
+        <v>1734817395.908</v>
       </c>
     </row>
     <row r="39">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="C39">
-        <v>22861.429</v>
+        <v>20871.641</v>
       </c>
       <c r="D39">
-        <v>20389.719</v>
+        <v>18504.427</v>
       </c>
       <c r="E39">
-        <v>25333.139</v>
+        <v>23238.855</v>
       </c>
       <c r="F39">
-        <v>8906.635</v>
+        <v>9384.91</v>
       </c>
       <c r="G39">
-        <v>7853.238</v>
+        <v>8261.346</v>
       </c>
       <c r="H39">
-        <v>9960.031000000001</v>
+        <v>10508.474</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2241,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>1184582394.841</v>
+        <v>1248192999.126</v>
       </c>
       <c r="M39">
-        <v>1044480667.873</v>
+        <v>1098758958.62</v>
       </c>
       <c r="N39">
-        <v>1324684121.808</v>
+        <v>1397627039.633</v>
       </c>
     </row>
     <row r="40">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="C40">
-        <v>22029.123</v>
+        <v>19554.173</v>
       </c>
       <c r="D40">
-        <v>19863.057</v>
+        <v>17550.77</v>
       </c>
       <c r="E40">
-        <v>24195.188</v>
+        <v>21557.576</v>
       </c>
       <c r="F40">
-        <v>6433.228</v>
+        <v>6606.248</v>
       </c>
       <c r="G40">
-        <v>5743.578</v>
+        <v>5894.2</v>
       </c>
       <c r="H40">
-        <v>7122.878</v>
+        <v>7318.297</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>855619354.455</v>
+        <v>878631020.518</v>
       </c>
       <c r="M40">
-        <v>763895877.086</v>
+        <v>783928569.924</v>
       </c>
       <c r="N40">
-        <v>947342831.824</v>
+        <v>973333471.113</v>
       </c>
     </row>
     <row r="41">
@@ -2310,22 +2310,22 @@
         </is>
       </c>
       <c r="C41">
-        <v>27174.477</v>
+        <v>23368.369</v>
       </c>
       <c r="D41">
-        <v>24917.933</v>
+        <v>21309.668</v>
       </c>
       <c r="E41">
-        <v>29431.021</v>
+        <v>25427.069</v>
       </c>
       <c r="F41">
-        <v>5439.667</v>
+        <v>5402.282</v>
       </c>
       <c r="G41">
-        <v>4935.977</v>
+        <v>4894.383</v>
       </c>
       <c r="H41">
-        <v>5943.356</v>
+        <v>5910.181</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2337,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>723475658.411</v>
+        <v>718503458.998</v>
       </c>
       <c r="M41">
-        <v>656484953.552</v>
+        <v>650952906.808</v>
       </c>
       <c r="N41">
-        <v>790466363.27</v>
+        <v>786054011.189</v>
       </c>
     </row>
     <row r="42">
@@ -2358,22 +2358,22 @@
         </is>
       </c>
       <c r="C42">
-        <v>17889.948</v>
+        <v>15055.729</v>
       </c>
       <c r="D42">
-        <v>16224.938</v>
+        <v>13533.284</v>
       </c>
       <c r="E42">
-        <v>19554.958</v>
+        <v>16578.175</v>
       </c>
       <c r="F42">
-        <v>1949.516</v>
+        <v>1863.928</v>
       </c>
       <c r="G42">
-        <v>1728.939</v>
+        <v>1642.971</v>
       </c>
       <c r="H42">
-        <v>2170.092</v>
+        <v>2084.885</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>259285579.977</v>
+        <v>247902435.888</v>
       </c>
       <c r="M42">
-        <v>229948940.24</v>
+        <v>218515128.253</v>
       </c>
       <c r="N42">
-        <v>288622219.714</v>
+        <v>277289743.523</v>
       </c>
     </row>
     <row r="43">
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="C43">
-        <v>7836.06</v>
+        <v>6261.993</v>
       </c>
       <c r="D43">
-        <v>6813.559</v>
+        <v>5312.951</v>
       </c>
       <c r="E43">
-        <v>8858.561</v>
+        <v>7211.035</v>
       </c>
       <c r="F43">
-        <v>152.736</v>
+        <v>142.903</v>
       </c>
       <c r="G43">
-        <v>121.215</v>
+        <v>108.957</v>
       </c>
       <c r="H43">
-        <v>184.257</v>
+        <v>176.849</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>20313886.808</v>
+        <v>19006046.404</v>
       </c>
       <c r="M43">
-        <v>16121609.306</v>
+        <v>14491226.848</v>
       </c>
       <c r="N43">
-        <v>24506164.309</v>
+        <v>23520865.96</v>
       </c>
     </row>
   </sheetData>
